--- a/data/trans_dic/IP24_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,69%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 15,52</t>
+          <t>7,43; 19,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 17,4</t>
+          <t>7,08; 15,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,71; 14,75</t>
+          <t>8,2; 15,76</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 11,15</t>
+          <t>5,42; 11,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,95; 10,73</t>
+          <t>5,28; 11,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 9,88</t>
+          <t>6,01; 10,57</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 12,64</t>
+          <t>8,91; 20,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,1; 18,4</t>
+          <t>3,03; 9,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,23; 13,08</t>
+          <t>7,12; 13,38</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 15,52</t>
+          <t>16,1; 27,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,48; 27,81</t>
+          <t>7,48; 15,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,03; 19,87</t>
+          <t>13,38; 20,18</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,76; 10,96</t>
+          <t>11,37; 16,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,71; 15,15</t>
+          <t>7,13; 10,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,27; 12,27</t>
+          <t>9,79; 12,88</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12384</t>
+          <t>15911</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15806</t>
+          <t>12868</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28191</t>
+          <t>28780</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8487; 18145</t>
+          <t>9324; 24695</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9406; 24344</t>
+          <t>8546; 18308</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19787; 37878</t>
+          <t>20190; 38818</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>24</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>14345</t>
+          <t>19061</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>14847</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33582</t>
+          <t>33908</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8991; 21245</t>
+          <t>12785; 27975</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12566; 27224</t>
+          <t>9730; 21370</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25303; 43895</t>
+          <t>25275; 44427</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11193</t>
+          <t>22806</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23065</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34258</t>
+          <t>31820</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5622; 23962</t>
+          <t>14836; 33480</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14818; 33646</t>
+          <t>4737; 14872</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23198; 48725</t>
+          <t>22963; 43167</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>17924</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38681</t>
+          <t>18279</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>56605</t>
+          <t>54820</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12262; 25898</t>
+          <t>27265; 45845</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29862; 50405</t>
+          <t>12430; 26415</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>45365; 69146</t>
+          <t>44910; 67717</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>55847</t>
+          <t>94319</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44882; 72726</t>
+          <t>79290; 113187</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>81121; 114773</t>
+          <t>44740; 67125</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>131762; 174382</t>
+          <t>129735; 170692</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP24_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP24_R_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que hacen entrenamiento deportivo o físico varias veces por semana (tasa de respuesta: 99,43%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10,66%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11,69%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>7,43; 19,68</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7,08; 15,16</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>8,2; 15,76</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>8,08%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8,05%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>8,07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>5,42; 11,86</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5,28; 11,59</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6,01; 10,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>9,86%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>8,91; 20,11</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3,03; 9,52</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7,12; 13,38</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>21,57%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>11,0%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>16,1; 27,07</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>7,48; 15,9</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>13,38; 20,18</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>13,53%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>11,37; 16,23</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7,13; 10,7</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>9,79; 12,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.1267963063709348</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.1065741254765901</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.1168799432236487</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>15911</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>12868</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28780</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.07430590682595076</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.07077921017224223</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.08199428241160496</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>9324; 24695</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>8546; 18308</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20190; 38818</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1967943949702263</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1516281626129381</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1576477353806565</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.08079484395379408</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.08050943075461273</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.08066962490613673</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>19061</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14847</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>33908</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.05419097873015801</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.05276104815188803</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.06013022729794695</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>12785; 27975</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>9730; 21370</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>25275; 44427</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.1185789281134872</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1158823314480745</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.1056946723282518</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.1370202508123836</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.05770526377239011</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.09862128731799746</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>22806</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9014</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>31820</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.08913463307981401</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.03032833350290198</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.07117027347260901</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>14836; 33480</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4737; 14872</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>22963; 43167</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.2011471531423814</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.095209420853186</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.1337908154415039</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.2157376554069735</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.1100090171872587</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1633800706688533</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>36541</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>18279</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>54820</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.1609747012842307</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.07480900740829119</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.1338451972101433</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>27265; 45845</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>12430; 26415</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>44910; 67717</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.2706679028023761</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.1589750209902283</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.2018186526356936</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.1352778258670091</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.08765936611695602</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1127213983778644</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>94319</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>55008</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>149328</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.1137212710526864</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.07129659071047194</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.09793194771502396</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>79290; 113187</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>44740; 67125</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>129735; 170692</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1623384425302957</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.1069691538419971</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.1288486158986255</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que hacen entrenamiento deportivo o físico varias veces por semana (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>15911</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>12868</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>28780</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>9324</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>8546</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>20190</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>24695</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>18308</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>38818</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>19061</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>14847</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>33908</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>12785</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>9730</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>25275</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>27975</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>21370</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>44427</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>22806</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>9014</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>31820</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>14836</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>4737</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>22963</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>33480</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>14872</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>43167</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>36541</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>18279</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>54820</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>27265</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>12430</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>44910</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>45845</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>26415</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>67717</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>94319</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>55008</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>149328</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>79290</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>44740</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>129735</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>113187</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>67125</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>170692</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>